--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2512448_1ºEA1ºEBFINAL_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2512448_1ºEA1ºEBFINAL_PROCESSED.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.0812</v>
+        <v>6.0475</v>
       </c>
       <c r="E2" t="n">
-        <v>3.8158</v>
+        <v>4.8711</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2654</v>
+        <v>1.1764</v>
       </c>
       <c r="G2" t="n">
-        <v>2.7673</v>
+        <v>2.7211</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5522</v>
+        <v>-0.6425999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>3.3195</v>
+        <v>3.3637</v>
       </c>
       <c r="J2" t="n">
-        <v>3.9051</v>
+        <v>4.0275</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2199</v>
+        <v>0.2258</v>
       </c>
       <c r="L2" t="n">
-        <v>3.6852</v>
+        <v>3.8018</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.1378</v>
+        <v>-1.3064</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.7721</v>
+        <v>-0.8683999999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.3657</v>
+        <v>-0.4381</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.0265</v>
+        <v>0.0217</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.2891</v>
+        <v>-0.3775</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2626</v>
+        <v>0.3991</v>
       </c>
       <c r="V2" t="n">
-        <v>1.5399</v>
+        <v>1.5521</v>
       </c>
       <c r="W2" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X2" t="n">
-        <v>0.3401</v>
+        <v>0.3311</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9333</v>
+        <v>4.863</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4667</v>
+        <v>3.8163</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4666</v>
+        <v>1.0467</v>
       </c>
       <c r="G3" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.09569999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.2855</v>
+        <v>-1.2125</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2954</v>
+        <v>1.3082</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5547</v>
+        <v>0.785</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.8489</v>
+        <v>-0.6823</v>
       </c>
       <c r="L3" t="n">
-        <v>1.4036</v>
+        <v>1.4673</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5447</v>
+        <v>-0.6893</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4366</v>
+        <v>-0.5302</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1082</v>
+        <v>-0.1591</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.4001</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4644</v>
+        <v>1.2141</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4536</v>
+        <v>0.4255</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0108</v>
+        <v>0.7886</v>
       </c>
       <c r="V3" t="n">
-        <v>3.8591</v>
+        <v>3.9426</v>
       </c>
       <c r="W3" t="n">
-        <v>4.459</v>
+        <v>4.5532</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5999</v>
+        <v>-0.6105</v>
       </c>
     </row>
     <row r="4">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.9245</v>
+        <v>4.4657</v>
       </c>
       <c r="E4" t="n">
-        <v>3.6336</v>
+        <v>3.2991</v>
       </c>
       <c r="F4" t="n">
-        <v>1.291</v>
+        <v>1.1665</v>
       </c>
       <c r="G4" t="n">
-        <v>3.0219</v>
+        <v>3.059</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5773</v>
+        <v>0.6179</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4446</v>
+        <v>2.4411</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5667</v>
+        <v>3.743</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8852</v>
+        <v>1.0033</v>
       </c>
       <c r="L4" t="n">
-        <v>2.6815</v>
+        <v>2.7397</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5448</v>
+        <v>-0.6841</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3079</v>
+        <v>-0.3855</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2369</v>
+        <v>-0.2986</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5623</v>
+        <v>1.102</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0671</v>
+        <v>0.5298</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4951</v>
+        <v>0.5722</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. MARTIN FERNANDEZ</t>
+          <t>J. DALMAU ROIG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5162</v>
+        <v>1.3434</v>
       </c>
       <c r="E5" t="n">
-        <v>7.2948</v>
+        <v>3.5023</v>
       </c>
       <c r="F5" t="n">
-        <v>-5.7786</v>
+        <v>-2.1589</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4622</v>
+        <v>-0.5382</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8951</v>
+        <v>-1.639</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.4329</v>
+        <v>1.1008</v>
       </c>
       <c r="J5" t="n">
-        <v>4.1626</v>
+        <v>2.0736</v>
       </c>
       <c r="K5" t="n">
-        <v>2.8028</v>
+        <v>-0.5285</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3598</v>
+        <v>2.602</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.7005</v>
+        <v>-2.6118</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9077</v>
+        <v>-1.1105</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.7927</v>
+        <v>-1.5013</v>
       </c>
       <c r="P5" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S5" t="n">
-        <v>3.2532</v>
+        <v>0.6684</v>
       </c>
       <c r="T5" t="n">
-        <v>3.1322</v>
+        <v>0.2077</v>
       </c>
       <c r="U5" t="n">
-        <v>0.121</v>
+        <v>0.4608</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.9994</v>
+        <v>0.4342</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.2211</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.9994</v>
+        <v>-0.7869</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. DALMAU ROIG</t>
+          <t>L. VERDEGUER FERRER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2956</v>
+        <v>-0.1016</v>
       </c>
       <c r="E6" t="n">
-        <v>3.2449</v>
+        <v>0.7373</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.9493</v>
+        <v>-0.8389</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5604</v>
+        <v>1.2135</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.6334</v>
+        <v>-0.3002</v>
       </c>
       <c r="I6" t="n">
-        <v>1.073</v>
+        <v>1.5138</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9472</v>
+        <v>1.0016</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5762</v>
+        <v>0.6774</v>
       </c>
       <c r="L6" t="n">
-        <v>2.5234</v>
+        <v>0.3242</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.5076</v>
+        <v>0.2119</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0571</v>
+        <v>-0.9776</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.4505</v>
+        <v>1.1896</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8002</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5551</v>
+        <v>0.9575</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0979</v>
+        <v>0.1504</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4572</v>
+        <v>0.8071</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5007</v>
+        <v>-1.8832</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1998</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6991000000000001</v>
+        <v>-2.4421</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. VERDEGUER FERRER</t>
+          <t>J. MARTIN FERNANDEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7281</v>
+        <v>-0.3595</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0816</v>
+        <v>5.7987</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3535</v>
+        <v>-6.1583</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2855</v>
+        <v>0.4737</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2617</v>
+        <v>1.9392</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5472</v>
+        <v>-1.4655</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9798</v>
+        <v>4.3184</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6598000000000001</v>
+        <v>2.9405</v>
       </c>
       <c r="L7" t="n">
-        <v>0.32</v>
+        <v>1.3779</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3057</v>
+        <v>-3.8447</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9215</v>
+        <v>-1.0013</v>
       </c>
       <c r="O7" t="n">
-        <v>1.2273</v>
+        <v>-2.8434</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.4001</v>
+        <v>0.7789</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0003</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6002</v>
+        <v>0.7789</v>
       </c>
       <c r="S7" t="n">
-        <v>1.7227</v>
+        <v>1.4404</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5825</v>
+        <v>1.4804</v>
       </c>
       <c r="U7" t="n">
-        <v>1.1402</v>
+        <v>-0.0399</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.88</v>
+        <v>-3.0526</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5196</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.3995</v>
+        <v>-3.0526</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>H. MARTORELL TRONCHONI</t>
+          <t>P. SILLA TEBAR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.7339</v>
+        <v>-1.3557</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0892</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6447000000000001</v>
+        <v>-1.2697</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.7529</v>
+        <v>0.4292</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6242</v>
+        <v>-0.4105</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1287</v>
+        <v>0.8397</v>
       </c>
       <c r="J8" t="n">
-        <v>0.04</v>
+        <v>2.6856</v>
       </c>
       <c r="K8" t="n">
-        <v>0.04</v>
+        <v>0.0591</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.6265</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7929</v>
+        <v>-2.2564</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6642</v>
+        <v>-0.4696</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1287</v>
+        <v>-1.7868</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.6002</v>
+        <v>-2.7263</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0003</v>
+        <v>-3.8947</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4001</v>
+        <v>1.1684</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3808</v>
+        <v>0.3309</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1289</v>
+        <v>-0.3775</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2519</v>
+        <v>0.7083</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.6105</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.5005</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. SILLA TEBAR</t>
+          <t>H. MARTORELL TRONCHONI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1327</v>
+        <v>-1.7139</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3399</v>
+        <v>-1.0563</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7927999999999999</v>
+        <v>-0.6576</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4244</v>
+        <v>-0.7866</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3999</v>
+        <v>-0.6471</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8243</v>
+        <v>-0.1395</v>
       </c>
       <c r="J9" t="n">
-        <v>2.4908</v>
+        <v>0.0411</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.0346</v>
+        <v>0.0411</v>
       </c>
       <c r="L9" t="n">
-        <v>2.5254</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.0664</v>
+        <v>-0.8276</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3653</v>
+        <v>-0.6882</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.7011</v>
+        <v>-0.1395</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.8008</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.0011</v>
+        <v>-0.9737</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2003</v>
+        <v>0.3895</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3562</v>
+        <v>-0.3431</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.2891</v>
+        <v>-0.1237</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9329</v>
+        <v>-0.2194</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5999</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.4596</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.8597</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.129</v>
+        <v>-1.8824</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.032</v>
+        <v>1.1484</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.097</v>
+        <v>-3.0308</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4574</v>
+        <v>0.491</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7198</v>
+        <v>0.7389</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2624</v>
+        <v>-0.2479</v>
       </c>
       <c r="J10" t="n">
-        <v>3.5648</v>
+        <v>3.7186</v>
       </c>
       <c r="K10" t="n">
-        <v>2.2412</v>
+        <v>2.3323</v>
       </c>
       <c r="L10" t="n">
-        <v>1.3236</v>
+        <v>1.3863</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.1074</v>
+        <v>-3.2276</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.5214</v>
+        <v>-1.5934</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.5861</v>
+        <v>-1.6342</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.2006</v>
+        <v>-2.1421</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.0009</v>
+        <v>-2.921</v>
       </c>
       <c r="R10" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0456</v>
+        <v>0.0997</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5157</v>
+        <v>0.4024</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.53</v>
+        <v>-0.3027</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3401</v>
+        <v>-0.3311</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.0803</v>
+        <v>-0.0516</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>V. PELUFO LOZANO</t>
+          <t>M. RODILLA ALCAIDE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7182</v>
+        <v>-3.5379</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5314</v>
+        <v>-0.7507</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.2496</v>
+        <v>-2.7872</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.2154</v>
+        <v>-1.2406</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2207</v>
+        <v>-0.6297</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.9948</v>
+        <v>-0.6109</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6852</v>
+        <v>1.7818</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5653</v>
+        <v>0.4926</v>
       </c>
       <c r="L11" t="n">
-        <v>0.12</v>
+        <v>1.2891</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.9007</v>
+        <v>-3.0223</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7859</v>
+        <v>-1.1223</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.1147</v>
+        <v>-1.9</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.0003</v>
+        <v>-2.5316</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.0006</v>
+        <v>-2.921</v>
       </c>
       <c r="R11" t="n">
-        <v>1.0003</v>
+        <v>0.3895</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0974</v>
+        <v>0.2342</v>
       </c>
       <c r="T11" t="n">
-        <v>0.647</v>
+        <v>0.3886</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5496</v>
+        <v>-0.1544</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.5999</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1998</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.7997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. RODILLA ALCAIDE</t>
+          <t>V. PELUFO LOZANO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.3784</v>
+        <v>-4.0965</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.6377</v>
+        <v>0.2206</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.7406</v>
+        <v>-4.3171</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.2221</v>
+        <v>-2.2271</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5704</v>
+        <v>-0.1698</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6516999999999999</v>
+        <v>-2.0573</v>
       </c>
       <c r="J12" t="n">
-        <v>1.6854</v>
+        <v>0.7965</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4799</v>
+        <v>0.6749000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>1.2055</v>
+        <v>0.1216</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.9075</v>
+        <v>-3.0236</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.0502</v>
+        <v>-0.8447</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.8573</v>
+        <v>-2.1789</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.6007</v>
+        <v>-0.9737</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.0009</v>
+        <v>-1.9474</v>
       </c>
       <c r="R12" t="n">
-        <v>0.4001</v>
+        <v>0.9737</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5555</v>
+        <v>-0.2852</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3223</v>
+        <v>0.1504</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2332</v>
+        <v>-0.4356</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-0.6105</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.2211</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.8316</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.386699999999998</v>
+        <v>3.672099999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>18.97</v>
+        <v>21.5008</v>
       </c>
       <c r="F13" t="n">
-        <v>-15.5831</v>
+        <v>-17.8289</v>
       </c>
       <c r="G13" t="n">
-        <v>3.6778</v>
+        <v>3.690700000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.3558</v>
+        <v>-2.355399999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>6.0335</v>
+        <v>6.046200000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>23.5823</v>
+        <v>24.9727</v>
       </c>
       <c r="K13" t="n">
-        <v>6.434399999999999</v>
+        <v>7.2362</v>
       </c>
       <c r="L13" t="n">
-        <v>17.148</v>
+        <v>17.7364</v>
       </c>
       <c r="M13" t="n">
-        <v>-19.9046</v>
+        <v>-21.2819</v>
       </c>
       <c r="N13" t="n">
-        <v>-8.789899999999999</v>
+        <v>-9.591699999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-11.1146</v>
+        <v>-11.6903</v>
       </c>
       <c r="P13" t="n">
-        <v>-6.0017</v>
+        <v>-5.8423</v>
       </c>
       <c r="Q13" t="n">
-        <v>-17.005</v>
+        <v>-16.5526</v>
       </c>
       <c r="R13" t="n">
-        <v>11.0031</v>
+        <v>10.7104</v>
       </c>
       <c r="S13" t="n">
-        <v>5.2905</v>
+        <v>5.440600000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>2.4352</v>
+        <v>2.8565</v>
       </c>
       <c r="U13" t="n">
-        <v>2.855099999999999</v>
+        <v>2.5841</v>
       </c>
       <c r="V13" t="n">
-        <v>0.4204000000000002</v>
+        <v>0.3824999999999996</v>
       </c>
       <c r="W13" t="n">
-        <v>9.9573</v>
+        <v>10.2244</v>
       </c>
       <c r="X13" t="n">
-        <v>-9.536799999999999</v>
+        <v>-9.8416</v>
       </c>
     </row>
     <row r="14">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.1099</v>
+        <v>4.0433</v>
       </c>
       <c r="E14" t="n">
-        <v>7.1985</v>
+        <v>6.5602</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.0885</v>
+        <v>-2.5168</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.2232</v>
+        <v>-0.1509</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.0964</v>
+        <v>-0.0359</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1268</v>
+        <v>-0.115</v>
       </c>
       <c r="J14" t="n">
-        <v>3.6704</v>
+        <v>3.9056</v>
       </c>
       <c r="K14" t="n">
-        <v>1.1469</v>
+        <v>1.3036</v>
       </c>
       <c r="L14" t="n">
-        <v>2.5234</v>
+        <v>2.602</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.8935</v>
+        <v>-4.0565</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.2433</v>
+        <v>-1.3394</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.6503</v>
+        <v>-2.7171</v>
       </c>
       <c r="P14" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R14" t="n">
-        <v>2.4007</v>
+        <v>2.3368</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4137</v>
+        <v>-0.7806</v>
       </c>
       <c r="T14" t="n">
-        <v>1.0094</v>
+        <v>0.0166</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5957</v>
+        <v>-0.7972</v>
       </c>
       <c r="V14" t="n">
-        <v>3.519</v>
+        <v>3.6116</v>
       </c>
       <c r="W14" t="n">
-        <v>3.519</v>
+        <v>3.6116</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.2829</v>
+        <v>1.8869</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0962</v>
+        <v>0.7644</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1867</v>
+        <v>1.1225</v>
       </c>
       <c r="G15" t="n">
-        <v>2.0132</v>
+        <v>2.0311</v>
       </c>
       <c r="H15" t="n">
-        <v>1.224</v>
+        <v>1.2629</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7892</v>
+        <v>0.7682</v>
       </c>
       <c r="J15" t="n">
-        <v>1.9214</v>
+        <v>1.9955</v>
       </c>
       <c r="K15" t="n">
-        <v>1.2814</v>
+        <v>1.3471</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6399</v>
+        <v>0.6484</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0919</v>
+        <v>0.0356</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0574</v>
+        <v>-0.0842</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1493</v>
+        <v>0.1198</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.8005</v>
+        <v>-1.7526</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.0009</v>
+        <v>-2.921</v>
       </c>
       <c r="R15" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1302</v>
+        <v>0.6667999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9759</v>
+        <v>0.4689</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1542</v>
+        <v>0.198</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9416</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. DE LA CAL DOMINGUEZ</t>
+          <t>M. TORTAROLO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9358</v>
+        <v>0.8835</v>
       </c>
       <c r="E16" t="n">
-        <v>3.813</v>
+        <v>3.6339</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.8772</v>
+        <v>-2.7504</v>
       </c>
       <c r="G16" t="n">
-        <v>1.2841</v>
+        <v>0.6405999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8041</v>
+        <v>0.7866</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4799</v>
+        <v>-0.146</v>
       </c>
       <c r="J16" t="n">
-        <v>3.5067</v>
+        <v>4.7891</v>
       </c>
       <c r="K16" t="n">
-        <v>1.5832</v>
+        <v>1.401</v>
       </c>
       <c r="L16" t="n">
-        <v>1.9235</v>
+        <v>3.3881</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.2226</v>
+        <v>-4.1485</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.779</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.4436</v>
+        <v>-3.5342</v>
       </c>
       <c r="P16" t="n">
-        <v>1.0003</v>
+        <v>1.5579</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.2001</v>
+        <v>-1.1684</v>
       </c>
       <c r="R16" t="n">
-        <v>1.2003</v>
+        <v>2.7263</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1487</v>
+        <v>-1.874</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3533</v>
+        <v>-1.1047</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2046</v>
+        <v>-0.7693</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.1998</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="W16" t="n">
-        <v>0.8597</v>
+        <v>1.1179</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.0594</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. TORTAROLO</t>
+          <t>A. DE LA CAL DOMINGUEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8073</v>
+        <v>0.628</v>
       </c>
       <c r="E17" t="n">
-        <v>3.4012</v>
+        <v>3.9533</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.5939</v>
+        <v>-3.3252</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6874</v>
+        <v>1.3182</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8092</v>
+        <v>0.8318</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1219</v>
+        <v>0.4863</v>
       </c>
       <c r="J17" t="n">
-        <v>4.6247</v>
+        <v>3.6825</v>
       </c>
       <c r="K17" t="n">
-        <v>1.3032</v>
+        <v>1.6884</v>
       </c>
       <c r="L17" t="n">
-        <v>3.3214</v>
+        <v>1.9942</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.9373</v>
+        <v>-2.3644</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.494</v>
+        <v>-0.8565</v>
       </c>
       <c r="O17" t="n">
-        <v>-3.4433</v>
+        <v>-1.5078</v>
       </c>
       <c r="P17" t="n">
-        <v>1.6005</v>
+        <v>0.9737</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.2003</v>
+        <v>-0.1947</v>
       </c>
       <c r="R17" t="n">
-        <v>2.8008</v>
+        <v>1.1684</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.0001</v>
+        <v>-0.4428</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0623</v>
+        <v>-0.4245</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9378</v>
+        <v>-0.0182</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5196</v>
+        <v>-1.2211</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0392</v>
+        <v>0.89</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5196</v>
+        <v>-2.1111</v>
       </c>
     </row>
     <row r="18">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7957</v>
+        <v>0.0121</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0091</v>
+        <v>0.6176</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2133</v>
+        <v>-0.6055</v>
       </c>
       <c r="G18" t="n">
-        <v>2.4758</v>
+        <v>2.4722</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3178</v>
+        <v>1.3214</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1579</v>
+        <v>1.1508</v>
       </c>
       <c r="J18" t="n">
-        <v>2.1632</v>
+        <v>2.2668</v>
       </c>
       <c r="K18" t="n">
-        <v>1.5614</v>
+        <v>1.6344</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6018</v>
+        <v>0.6323</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3126</v>
+        <v>0.2054</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2435</v>
+        <v>-0.3131</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5561</v>
+        <v>0.5185</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.2006</v>
+        <v>-2.1421</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.0009</v>
+        <v>-2.921</v>
       </c>
       <c r="R18" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7804</v>
+        <v>-0.0385</v>
       </c>
       <c r="T18" t="n">
-        <v>0.647</v>
+        <v>0.0508</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1334</v>
+        <v>-0.0893</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.4596</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="19">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0887</v>
+        <v>-0.6254</v>
       </c>
       <c r="E19" t="n">
-        <v>3.4954</v>
+        <v>4.2375</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.5841</v>
+        <v>-4.8629</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2346</v>
+        <v>0.1404</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0698</v>
+        <v>-0.1725</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3043</v>
+        <v>0.3129</v>
       </c>
       <c r="J19" t="n">
-        <v>5.0429</v>
+        <v>5.1705</v>
       </c>
       <c r="K19" t="n">
-        <v>1.1597</v>
+        <v>1.1905</v>
       </c>
       <c r="L19" t="n">
-        <v>3.8833</v>
+        <v>3.9799</v>
       </c>
       <c r="M19" t="n">
-        <v>-4.8084</v>
+        <v>-5.0301</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2294</v>
+        <v>-1.3631</v>
       </c>
       <c r="O19" t="n">
-        <v>-3.5789</v>
+        <v>-3.6671</v>
       </c>
       <c r="P19" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="R19" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.3236</v>
+        <v>-1.7395</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.547</v>
+        <v>-0.9857</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7766</v>
+        <v>-0.7538</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="20">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1698</v>
+        <v>-1.367</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5463</v>
+        <v>0.4126</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6235</v>
+        <v>-1.7796</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.5269</v>
+        <v>-0.5103</v>
       </c>
       <c r="H20" t="n">
-        <v>1.8446</v>
+        <v>1.8432</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.3715</v>
+        <v>-2.3535</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3672</v>
+        <v>0.4936</v>
       </c>
       <c r="K20" t="n">
-        <v>2.3593</v>
+        <v>2.4221</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.9921</v>
+        <v>-1.9286</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8941</v>
+        <v>-1.0038</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5147</v>
+        <v>-0.5789</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3794</v>
+        <v>-0.4249</v>
       </c>
       <c r="P20" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5037</v>
+        <v>0.3586</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5734</v>
+        <v>0.2501</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0697</v>
+        <v>0.1084</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.7396</v>
+        <v>-2.7732</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3401</v>
+        <v>-0.3311</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.3995</v>
+        <v>-2.4421</v>
       </c>
     </row>
     <row r="21">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.7624</v>
+        <v>-1.9434</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1122</v>
+        <v>0.9089</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.8746</v>
+        <v>-2.8523</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.9445</v>
+        <v>-1.9532</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.4196</v>
+        <v>-1.4574</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5249</v>
+        <v>-0.4958</v>
       </c>
       <c r="J21" t="n">
-        <v>1.871</v>
+        <v>2.0493</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6544</v>
+        <v>-0.5772</v>
       </c>
       <c r="L21" t="n">
-        <v>2.5254</v>
+        <v>2.6265</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.8154</v>
+        <v>-4.0025</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7652</v>
+        <v>-0.8802</v>
       </c>
       <c r="O21" t="n">
-        <v>-3.0502</v>
+        <v>-3.1223</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.2777</v>
+        <v>-1.4644</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.418</v>
+        <v>-0.862</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8597</v>
+        <v>-0.6025</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8597</v>
+        <v>0.89</v>
       </c>
       <c r="W21" t="n">
-        <v>0.8597</v>
+        <v>0.89</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8873</v>
+        <v>-2.3795</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.7787</v>
+        <v>-2.2128</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1086</v>
+        <v>-0.1668</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.4427</v>
+        <v>-2.4203</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.008699999999999999</v>
+        <v>-0.0216</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.4339</v>
+        <v>-2.3988</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.592</v>
+        <v>-2.5349</v>
       </c>
       <c r="K22" t="n">
-        <v>0.12</v>
+        <v>0.1232</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.712</v>
+        <v>-2.658</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1494</v>
+        <v>0.1145</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1287</v>
+        <v>-0.1447</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2781</v>
+        <v>0.2592</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1549</v>
+        <v>0.6777</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1867</v>
+        <v>0.3221</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3416</v>
+        <v>0.3556</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.4102</v>
+        <v>-4.5011</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.2174</v>
+        <v>-1.0466</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.1928</v>
+        <v>-3.4545</v>
       </c>
       <c r="G23" t="n">
-        <v>-5.2355</v>
+        <v>-5.2585</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.0496</v>
+        <v>-2.0033</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.1858</v>
+        <v>-3.2552</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6707</v>
+        <v>-0.5362</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.0707</v>
+        <v>-0.9415</v>
       </c>
       <c r="L23" t="n">
-        <v>0.3999</v>
+        <v>0.4053</v>
       </c>
       <c r="M23" t="n">
-        <v>-4.5647</v>
+        <v>-4.7223</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.979</v>
+        <v>-1.0618</v>
       </c>
       <c r="O23" t="n">
-        <v>-3.5858</v>
+        <v>-3.6605</v>
       </c>
       <c r="P23" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="R23" t="n">
-        <v>2.4007</v>
+        <v>2.3368</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5157</v>
+        <v>-0.4947</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3466</v>
+        <v>-0.3156</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.169</v>
+        <v>-0.1791</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.8597</v>
+        <v>-0.89</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.8597</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.3868</v>
+        <v>-3.3626</v>
       </c>
       <c r="E24" t="n">
-        <v>15.5832</v>
+        <v>17.829</v>
       </c>
       <c r="F24" t="n">
-        <v>-18.9698</v>
+        <v>-21.1915</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.6777</v>
+        <v>-3.6907</v>
       </c>
       <c r="H24" t="n">
-        <v>2.3556</v>
+        <v>2.3552</v>
       </c>
       <c r="I24" t="n">
-        <v>-6.0335</v>
+        <v>-6.046099999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>19.9048</v>
+        <v>21.2818</v>
       </c>
       <c r="K24" t="n">
-        <v>8.789999999999999</v>
+        <v>9.591600000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>11.1145</v>
+        <v>11.6901</v>
       </c>
       <c r="M24" t="n">
-        <v>-23.5821</v>
+        <v>-24.9726</v>
       </c>
       <c r="N24" t="n">
-        <v>-6.434200000000001</v>
+        <v>-7.2363</v>
       </c>
       <c r="O24" t="n">
-        <v>-17.148</v>
+        <v>-17.7364</v>
       </c>
       <c r="P24" t="n">
-        <v>6.001900000000001</v>
+        <v>5.8422</v>
       </c>
       <c r="Q24" t="n">
-        <v>-11.0032</v>
+        <v>-10.7103</v>
       </c>
       <c r="R24" t="n">
-        <v>17.0048</v>
+        <v>16.5524</v>
       </c>
       <c r="S24" t="n">
-        <v>-5.290299999999999</v>
+        <v>-5.1314</v>
       </c>
       <c r="T24" t="n">
-        <v>-2.855</v>
+        <v>-2.584</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.4353</v>
+        <v>-2.5474</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.4204</v>
+        <v>-0.3826999999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>9.536899999999999</v>
+        <v>9.841699999999999</v>
       </c>
       <c r="X24" t="n">
-        <v>-9.9572</v>
+        <v>-10.2244</v>
       </c>
     </row>
   </sheetData>
